--- a/personal_trainer_forms/001_fitness_liability_waiver--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/001_fitness_liability_waiver--personal_trainer_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Services Phone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Services Email</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Emergency Services Address</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
